--- a/data/trans_camb/P05B_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P05B_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,12</t>
+          <t>-1,25</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,0</t>
+          <t>-3,09</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,9</t>
+          <t>-2,01</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 2,09</t>
+          <t>-2,68; 2,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; -0,05</t>
+          <t>-4,02; 0,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,91</t>
+          <t>-3,31; 0,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,9; -1,49</t>
+          <t>-6,81; -1,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,55; -1,35</t>
+          <t>-6,57; -1,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,11; -0,79</t>
+          <t>-6,32; -0,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 0,12</t>
+          <t>-3,49; -0,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,15; -1,12</t>
+          <t>-4,33; -1,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,53; -0,42</t>
+          <t>-3,62; -0,32</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-34,24%</t>
+          <t>-38,0%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-64,75%</t>
+          <t>-66,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-49,88%</t>
+          <t>-52,74%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-61,51; 102,89</t>
+          <t>-60,81; 105,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-88,97; 12,7</t>
+          <t>-88,71; 32,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-73,64; 55,66</t>
+          <t>-77,32; 47,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -39,32</t>
+          <t>-100,0; -26,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-95,13; -24,31</t>
+          <t>-95,4; -31,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-87,69; -12,92</t>
+          <t>-87,07; -14,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-70,76; 7,81</t>
+          <t>-72,16; 1,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-87,43; -29,83</t>
+          <t>-87,25; -32,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-73,78; -7,35</t>
+          <t>-73,42; -7,94</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,73</t>
+          <t>-2,74</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,64</t>
+          <t>-1,82</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,24</t>
+          <t>-2,32</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 1,01</t>
+          <t>-4,04; 1,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,6; -0,96</t>
+          <t>-5,33; -0,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,37; -0,94</t>
+          <t>-5,25; -0,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 0,98</t>
+          <t>-3,92; 1,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 0,88</t>
+          <t>-4,02; 0,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 0,46</t>
+          <t>-4,46; 0,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 0,26</t>
+          <t>-3,25; 0,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; -0,74</t>
+          <t>-3,88; -0,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -0,89</t>
+          <t>-4,1; -0,93</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-83,65%</t>
+          <t>-83,93%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-46,44%</t>
+          <t>-51,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-65,97%</t>
+          <t>-68,16%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-85,02; 61,21</t>
+          <t>-83,88; 104,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 62,87</t>
+          <t>-100,0; 53,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-97,0; -23,85</t>
+          <t>-100,0; -26,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-80,12; 55,34</t>
+          <t>-80,5; 54,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,96; 59,71</t>
+          <t>-81,74; 61,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,86; 33,22</t>
+          <t>-83,05; 25,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-73,05; 16,06</t>
+          <t>-73,37; 22,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-86,57; -18,78</t>
+          <t>-85,56; -22,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-84,91; -29,0</t>
+          <t>-85,26; -34,22</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,39</t>
+          <t>-1,08</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,51</t>
+          <t>-5,3</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,36</t>
+          <t>-2,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,05</t>
+          <t>-2,61; -0,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,94; -0,09</t>
+          <t>-2,97; -0,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 0,2</t>
+          <t>-2,59; 0,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,35; -1,31</t>
+          <t>-9,67; -1,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,82; -3,12</t>
+          <t>-11,37; -3,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,28; -2,14</t>
+          <t>-10,51; -2,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,65; -0,81</t>
+          <t>-3,77; -0,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,13; -1,24</t>
+          <t>-4,1; -1,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,15; -1,05</t>
+          <t>-3,68; -0,75</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-65,52%</t>
+          <t>-51,25%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-87,98%</t>
+          <t>-84,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-76,29%</t>
+          <t>-67,29%</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1215,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-88,21; 24,9</t>
+          <t>-86,39; 8,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-95,24; 20,92</t>
+          <t>-94,06; 22,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-94,9; 19,5</t>
+          <t>-84,54; 51,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-96,18; -27,66</t>
+          <t>-100,0; -21,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-98,36; -41,71</t>
+          <t>-97,35; -41,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-87,98; -29,7</t>
+          <t>-87,93; -35,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-96,98; -37,94</t>
+          <t>-96,94; -45,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-94,24; -41,37</t>
+          <t>-87,64; -24,16</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,32</t>
+          <t>-2,41</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,67</t>
+          <t>-3,44</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,81</t>
+          <t>-2,77</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,81; -0,25</t>
+          <t>-2,96; -0,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,21</t>
+          <t>-2,44; 0,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,64; -1,2</t>
+          <t>-3,74; -1,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,13; -0,21</t>
+          <t>-4,24; -0,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,96; -0,12</t>
+          <t>-4,08; -0,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,54; -2,14</t>
+          <t>-5,2; -1,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,83; -0,62</t>
+          <t>-2,81; -0,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; -0,36</t>
+          <t>-2,65; -0,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -1,84</t>
+          <t>-3,76; -1,78</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-70,62%</t>
+          <t>-73,46%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-78,89%</t>
+          <t>-73,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-74,29%</t>
+          <t>-73,08%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-69,63; -5,69</t>
+          <t>-70,94; -8,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-63,15; 9,78</t>
+          <t>-60,84; 7,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-86,99; -42,61</t>
+          <t>-88,95; -49,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-70,31; -4,98</t>
+          <t>-70,5; -3,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-67,99; 1,9</t>
+          <t>-68,16; 1,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-91,66; -59,68</t>
+          <t>-86,69; -54,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-62,73; -18,81</t>
+          <t>-63,6; -19,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-57,55; -9,73</t>
+          <t>-58,49; -10,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-84,48; -55,13</t>
+          <t>-82,87; -53,98</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,94</t>
+          <t>-1,12</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,67</t>
+          <t>-3,6</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,62</t>
+          <t>-2,66</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 0,55</t>
+          <t>-3,09; 0,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,29</t>
+          <t>-2,32; 1,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,58</t>
+          <t>-3,06; 0,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,29; -2,16</t>
+          <t>-5,99; -2,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,71; -1,49</t>
+          <t>-5,34; -1,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,92; -1,89</t>
+          <t>-5,63; -1,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,43; -1,57</t>
+          <t>-4,37; -1,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,65; -0,82</t>
+          <t>-3,75; -0,82</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,06; -1,39</t>
+          <t>-4,07; -1,37</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-45,77%</t>
+          <t>-54,61%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-72,7%</t>
+          <t>-71,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-67,14%</t>
+          <t>-68,29%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-87,47; 87,61</t>
+          <t>-85,82; 82,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-73,85; 149,09</t>
+          <t>-73,85; 122,28</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-85,02; 95,14</t>
+          <t>-86,47; 50,83</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-93,15; -48,18</t>
+          <t>-91,88; -51,84</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-81,4; -33,09</t>
+          <t>-81,18; -25,21</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-85,47; -48,6</t>
+          <t>-84,26; -48,71</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-87,44; -47,3</t>
+          <t>-86,99; -45,87</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-74,13; -24,32</t>
+          <t>-74,1; -24,3</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-80,82; -45,5</t>
+          <t>-81,29; -44,86</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-4,04</t>
+          <t>-4,07</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-3,91</t>
+          <t>-3,93</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 1,04</t>
+          <t>-4,04; 0,86</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,53; -1,12</t>
+          <t>-5,54; -1,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,87; -1,62</t>
+          <t>-6,03; -1,63</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,46; -1,65</t>
+          <t>-4,56; -1,77</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,4; -0,29</t>
+          <t>-3,44; -0,38</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,43; -2,84</t>
+          <t>-5,41; -2,94</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,99; -1,44</t>
+          <t>-4,1; -1,47</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,36; -0,77</t>
+          <t>-3,48; -0,73</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,07; -2,9</t>
+          <t>-5,13; -2,89</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-86,02%</t>
+          <t>-86,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-88,7%</t>
+          <t>-89,09%</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-87,39; 94,47</t>
+          <t>-87,46; 68,44</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -22,34</t>
+          <t>-100,0; 14,02</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-79,95; -40,69</t>
+          <t>-79,78; -41,61</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-62,29; -6,02</t>
+          <t>-62,72; -6,88</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-93,67; -71,77</t>
+          <t>-94,12; -75,02</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-75,82; -37,14</t>
+          <t>-77,89; -38,74</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-67,59; -19,29</t>
+          <t>-67,05; -17,98</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-94,66; -77,58</t>
+          <t>-94,94; -79,23</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-1,96</t>
+          <t>-1,97</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-3,51</t>
+          <t>-3,47</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-2,75</t>
+          <t>-2,73</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,01; -0,56</t>
+          <t>-2,15; -0,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,32; -0,88</t>
+          <t>-2,41; -0,94</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,66; -1,21</t>
+          <t>-2,75; -1,36</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,9; -2,17</t>
+          <t>-3,92; -2,15</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,48; -1,7</t>
+          <t>-3,51; -1,66</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,33; -2,71</t>
+          <t>-4,22; -2,72</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,77; -1,64</t>
+          <t>-2,74; -1,62</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,59; -1,52</t>
+          <t>-2,71; -1,52</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,33; -2,25</t>
+          <t>-3,32; -2,23</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-66,42%</t>
+          <t>-66,77%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-74,97%</t>
+          <t>-74,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-71,7%</t>
+          <t>-71,25%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-59,9; -21,2</t>
+          <t>-61,52; -22,43</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-67,33; -33,3</t>
+          <t>-68,54; -34,93</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-78,45; -48,79</t>
+          <t>-78,3; -52,59</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-75,08; -52,16</t>
+          <t>-74,6; -52,67</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-66,1; -39,46</t>
+          <t>-66,67; -39,86</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-82,15; -66,36</t>
+          <t>-80,65; -64,46</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-66,28; -46,66</t>
+          <t>-66,18; -46,59</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-62,37; -41,65</t>
+          <t>-63,4; -42,3</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-78,65; -63,28</t>
+          <t>-77,83; -62,97</t>
         </is>
       </c>
     </row>
